--- a/fliad-plugin/plugin-dahua/model/dahua.orm.xlsx
+++ b/fliad-plugin/plugin-dahua/model/dahua.orm.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="目录" sheetId="1" r:id="rId1"/>
     <sheet name="配置" sheetId="2" r:id="rId2"/>
     <sheet name="域定义" sheetId="3" r:id="rId3"/>
     <sheet name="字典定义" sheetId="4" r:id="rId4"/>
-    <sheet name="HIKVISION_CAMERA" sheetId="22" r:id="rId5"/>
+    <sheet name="DAHUA_CAMERA" sheetId="22" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="143">
   <si>
     <t>序号</t>
   </si>
@@ -150,111 +150,186 @@
     <t>Java类型</t>
   </si>
   <si>
+    <t>userName</t>
+  </si>
+  <si>
+    <t>VARCHAR</t>
+  </si>
+  <si>
+    <t>image</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>roleId</t>
+  </si>
+  <si>
+    <t>userId</t>
+  </si>
+  <si>
+    <t>deptId</t>
+  </si>
+  <si>
+    <t>boolFlag</t>
+  </si>
+  <si>
+    <t>TINYINT</t>
+  </si>
+  <si>
+    <t>json-128K</t>
+  </si>
+  <si>
+    <t>json</t>
+  </si>
+  <si>
+    <t>128K</t>
+  </si>
+  <si>
+    <t>remark</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>INTEGER</t>
+  </si>
+  <si>
+    <t>createTime</t>
+  </si>
+  <si>
+    <t>TIMESTAMP</t>
+  </si>
+  <si>
+    <t>createdBy</t>
+  </si>
+  <si>
+    <t>updateTime</t>
+  </si>
+  <si>
+    <t>updatedBy</t>
+  </si>
+  <si>
+    <t>delFlag</t>
+  </si>
+  <si>
+    <t>BOOLEAN</t>
+  </si>
+  <si>
+    <t>mediumtext</t>
+  </si>
+  <si>
+    <t>wfAction</t>
+  </si>
+  <si>
+    <t>dahua/enableStatus</t>
+  </si>
+  <si>
+    <t>值类型</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>启用状态</t>
+  </si>
+  <si>
+    <t>英文名</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>字典项</t>
+  </si>
+  <si>
+    <t>值</t>
+  </si>
+  <si>
+    <t>代码</t>
+  </si>
+  <si>
+    <t>启用</t>
+  </si>
+  <si>
+    <t>禁用</t>
+  </si>
+  <si>
+    <t>DAHUA_CAMERA</t>
+  </si>
+  <si>
+    <t>对象名</t>
+  </si>
+  <si>
+    <t>DahuaCamera</t>
+  </si>
+  <si>
+    <t>大华设备表</t>
+  </si>
+  <si>
+    <t>标签</t>
+  </si>
+  <si>
+    <t>所属模块</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>字段列表</t>
+  </si>
+  <si>
+    <t>编号</t>
+  </si>
+  <si>
+    <t>主键</t>
+  </si>
+  <si>
+    <t>字段名</t>
+  </si>
+  <si>
+    <t>控件</t>
+  </si>
+  <si>
+    <t>显示</t>
+  </si>
+  <si>
+    <t>数据域</t>
+  </si>
+  <si>
+    <t>非空</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>字典</t>
+  </si>
+  <si>
+    <t>缺省值</t>
+  </si>
+  <si>
+    <t>扩展配置</t>
+  </si>
+  <si>
+    <t>PK</t>
+  </si>
+  <si>
+    <t>seq</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>dahua/enableStatus</t>
-  </si>
-  <si>
-    <t>值类型</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>启用状态</t>
-  </si>
-  <si>
-    <t>英文名</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>字典项</t>
-  </si>
-  <si>
-    <t>值</t>
-  </si>
-  <si>
-    <t>代码</t>
-  </si>
-  <si>
-    <t>启用</t>
-  </si>
-  <si>
-    <t>禁用</t>
-  </si>
-  <si>
-    <t>DAHUA_CAMERA</t>
-  </si>
-  <si>
-    <t>对象名</t>
-  </si>
-  <si>
-    <t>DahuaCamera</t>
-  </si>
-  <si>
-    <t>大华设备表</t>
-  </si>
-  <si>
-    <t>标签</t>
-  </si>
-  <si>
-    <t>所属模块</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>字段列表</t>
-  </si>
-  <si>
-    <t>编号</t>
-  </si>
-  <si>
-    <t>主键</t>
-  </si>
-  <si>
-    <t>字段名</t>
-  </si>
-  <si>
-    <t>控件</t>
-  </si>
-  <si>
-    <t>显示</t>
-  </si>
-  <si>
-    <t>数据域</t>
-  </si>
-  <si>
-    <t>非空</t>
-  </si>
-  <si>
-    <t>类型</t>
-  </si>
-  <si>
-    <t>字典</t>
-  </si>
-  <si>
-    <t>缺省值</t>
-  </si>
-  <si>
-    <t>扩展配置</t>
-  </si>
-  <si>
-    <t>PK</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>VARCHAR</t>
-  </si>
-  <si>
     <t>DEVICE_ID</t>
   </si>
   <si>
@@ -277,9 +352,6 @@
   </si>
   <si>
     <t>端口号</t>
-  </si>
-  <si>
-    <t>INTEGER</t>
   </si>
   <si>
     <t>USERNAME</t>
@@ -414,18 +486,18 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0563C1"/>
       <name val="等线"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -615,6 +687,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -766,12 +844,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1015,19 +1087,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1036,7 +1108,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1060,16 +1132,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1078,73 +1150,73 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1160,7 +1232,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1281,7 +1353,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="6" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1290,7 +1374,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1638,7 +1722,7 @@
       <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="43"/>
+      <c r="B2" s="47"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
     </row>
@@ -1646,7 +1730,7 @@
       <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="43"/>
+      <c r="B3" s="47"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
     </row>
@@ -1718,7 +1802,7 @@
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="41" t="b">
+      <c r="B2" s="45" t="b">
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -1729,7 +1813,7 @@
       <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="46" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -1740,7 +1824,7 @@
       <c r="A4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="46" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="5" t="s">
@@ -1751,7 +1835,7 @@
       <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="46" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -1762,7 +1846,7 @@
       <c r="A6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="46" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -1773,7 +1857,7 @@
       <c r="A7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="46" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="5" t="s">
@@ -1784,7 +1868,7 @@
       <c r="A8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="46" t="s">
         <v>23</v>
       </c>
       <c r="C8" s="5" t="s">
@@ -1795,7 +1879,7 @@
       <c r="A9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="46" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="5" t="s">
@@ -1806,7 +1890,7 @@
       <c r="A10" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="46" t="s">
         <v>28</v>
       </c>
       <c r="C10" s="5" t="s">
@@ -1858,232 +1942,391 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="4.91666666666667" customWidth="1"/>
-    <col min="2" max="4" width="8.5" customWidth="1"/>
+    <col min="2" max="2" width="12.75" customWidth="1"/>
+    <col min="3" max="3" width="8.5" customWidth="1"/>
+    <col min="4" max="4" width="11.75" customWidth="1"/>
     <col min="5" max="5" width="9.08333333333333" customWidth="1"/>
     <col min="6" max="7" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="40" t="s">
+      <c r="E1" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="40" t="s">
+      <c r="F1" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="40" t="s">
+      <c r="G1" s="41" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="3"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="A2" s="42">
+        <v>1</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="43">
+        <v>50</v>
+      </c>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
+      <c r="A3" s="42">
+        <v>2</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="43">
+        <v>100</v>
+      </c>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
+      <c r="A4" s="42">
+        <v>3</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="43">
+        <v>100</v>
+      </c>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
+      <c r="A5" s="42">
+        <v>4</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="43">
+        <v>100</v>
+      </c>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
+      <c r="A6" s="42">
+        <v>5</v>
+      </c>
+      <c r="B6" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="43">
+        <v>100</v>
+      </c>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
+      <c r="A7" s="42">
+        <v>6</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="43">
+        <v>50</v>
+      </c>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
+      <c r="A8" s="42">
+        <v>7</v>
+      </c>
+      <c r="B8" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="43">
+        <v>50</v>
+      </c>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
+      <c r="A9" s="42">
+        <v>8</v>
+      </c>
+      <c r="B9" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
+      <c r="A10" s="42">
+        <v>9</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
+      <c r="A11" s="42">
+        <v>10</v>
+      </c>
+      <c r="B11" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="43">
+        <v>1</v>
+      </c>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
+      <c r="A12" s="42">
+        <v>11</v>
+      </c>
+      <c r="B12" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
+      <c r="A13" s="42">
+        <v>12</v>
+      </c>
+      <c r="B13" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="A14" s="42">
+        <v>13</v>
+      </c>
+      <c r="B14" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="43">
+        <v>50</v>
+      </c>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+      <c r="A15" s="42">
+        <v>14</v>
+      </c>
+      <c r="B15" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
+      <c r="A16" s="42">
+        <v>15</v>
+      </c>
+      <c r="B16" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="43">
+        <v>50</v>
+      </c>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
+      <c r="A17" s="42">
+        <v>16</v>
+      </c>
+      <c r="B17" s="43" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
+      <c r="A18" s="42">
+        <v>17</v>
+      </c>
+      <c r="B18" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="44">
+        <v>16777215</v>
+      </c>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
+      <c r="A19" s="42">
+        <v>18</v>
+      </c>
+      <c r="B19" s="43" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="43">
+        <v>200</v>
+      </c>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="43"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="43"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="43"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="43"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="43"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="43"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2113,14 +2356,14 @@
       </c>
       <c r="C1" s="27"/>
       <c r="D1" s="28" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="E1" s="29"/>
       <c r="F1" s="26" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="G1" s="29" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -2130,18 +2373,18 @@
       </c>
       <c r="C2" s="27"/>
       <c r="D2" s="28" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="26" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="G2" s="3"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="30"/>
       <c r="B3" s="26" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="C3" s="27"/>
       <c r="D3" s="28"/>
@@ -2152,7 +2395,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="30"/>
       <c r="B4" s="32" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C4" s="33"/>
       <c r="D4" s="33"/>
@@ -2166,19 +2409,19 @@
         <v>0</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="D5" s="36" t="s">
         <v>33</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2190,7 +2433,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -2205,7 +2448,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -2269,17 +2512,17 @@
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="1" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
@@ -2297,14 +2540,14 @@
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="6" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
@@ -2318,7 +2561,7 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -2328,7 +2571,7 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="7" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
@@ -2342,7 +2585,7 @@
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -2384,7 +2627,7 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="9" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -2406,40 +2649,40 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="1" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>34</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>36</v>
@@ -2448,16 +2691,16 @@
         <v>37</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -2465,28 +2708,30 @@
         <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>95</v>
+      </c>
       <c r="D8" s="10" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="3"/>
       <c r="G8" s="10"/>
       <c r="H8" s="10" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
       <c r="K8" s="3" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="M8" s="3">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="N8" s="3"/>
       <c r="O8" s="10"/>
@@ -2499,25 +2744,25 @@
         <v>2</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="10" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="3"/>
       <c r="G9" s="10"/>
       <c r="H9" s="10" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
       <c r="K9" s="3" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="M9" s="3">
         <v>64</v>
@@ -2533,25 +2778,25 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="10" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="3"/>
       <c r="G10" s="10"/>
       <c r="H10" s="10" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
       <c r="K10" s="3" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="M10" s="3">
         <v>128</v>
@@ -2567,25 +2812,25 @@
         <v>4</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="10" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="3"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
       <c r="K11" s="3" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="M11" s="3">
         <v>64</v>
@@ -2601,25 +2846,25 @@
         <v>5</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="10" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="3"/>
       <c r="G12" s="10"/>
       <c r="H12" s="10" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
       <c r="K12" s="3" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
@@ -2633,25 +2878,25 @@
         <v>6</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="10" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="3"/>
       <c r="G13" s="10"/>
       <c r="H13" s="10" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
       <c r="K13" s="3" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="M13" s="3">
         <v>64</v>
@@ -2667,25 +2912,25 @@
         <v>7</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="10" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="3"/>
       <c r="G14" s="10"/>
       <c r="H14" s="10" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
       <c r="K14" s="3" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="M14" s="3">
         <v>128</v>
@@ -2701,35 +2946,35 @@
         <v>8</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="10" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="3"/>
       <c r="G15" s="10"/>
       <c r="H15" s="10" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
       <c r="K15" s="3" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="M15" s="3">
         <v>1</v>
       </c>
       <c r="N15" s="3"/>
       <c r="O15" s="10" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="Q15" s="3"/>
       <c r="R15" s="5"/>
@@ -2739,25 +2984,25 @@
         <v>9</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="10" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="3"/>
       <c r="G16" s="10"/>
       <c r="H16" s="10" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="I16" s="10"/>
       <c r="J16" s="10"/>
       <c r="K16" s="3" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="M16" s="3">
         <v>1</v>
@@ -2765,7 +3010,7 @@
       <c r="N16" s="3"/>
       <c r="O16" s="10"/>
       <c r="P16" s="10" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="Q16" s="3"/>
       <c r="R16" s="5"/>
@@ -2775,25 +3020,27 @@
         <v>10</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="10" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="E17" s="10"/>
       <c r="F17" s="3"/>
       <c r="G17" s="10"/>
       <c r="H17" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="I17" s="10"/>
+        <v>118</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="J17" s="10"/>
       <c r="K17" s="3" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
@@ -2807,25 +3054,27 @@
         <v>11</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="10" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="3"/>
       <c r="G18" s="10"/>
       <c r="H18" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="I18" s="10"/>
+        <v>121</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>58</v>
+      </c>
       <c r="J18" s="10"/>
       <c r="K18" s="3" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
@@ -2876,7 +3125,7 @@
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="9" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -2899,7 +3148,7 @@
     <row r="23" spans="1:18">
       <c r="A23" s="11"/>
       <c r="B23" s="1" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="3"/>
@@ -2907,14 +3156,14 @@
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="1" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="12" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="N23" s="12"/>
       <c r="O23" s="10"/>
@@ -2933,14 +3182,14 @@
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="12" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="N24" s="12"/>
       <c r="O24" s="10"/>
@@ -2951,7 +3200,7 @@
     <row r="25" spans="1:18">
       <c r="A25" s="11"/>
       <c r="B25" s="1" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="3"/>
@@ -2959,14 +3208,14 @@
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="13" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14"/>
       <c r="K25" s="14"/>
       <c r="L25" s="14"/>
       <c r="M25" s="12" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="N25" s="12"/>
       <c r="O25" s="10"/>
@@ -2977,7 +3226,7 @@
     <row r="26" spans="1:18">
       <c r="A26" s="11"/>
       <c r="B26" s="1" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="3"/>
@@ -2985,14 +3234,14 @@
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="1" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="12" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="N26" s="12"/>
       <c r="O26" s="10"/>
@@ -3003,7 +3252,7 @@
     <row r="27" spans="1:18">
       <c r="A27" s="11"/>
       <c r="B27" s="15" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="C27" s="15"/>
       <c r="D27" s="15"/>
@@ -3028,21 +3277,21 @@
         <v>0</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="D28" s="12"/>
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
       <c r="G28" s="17" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="I28" s="12"/>
       <c r="J28" s="18"/>
       <c r="K28" s="12" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="L28" s="12"/>
       <c r="M28" s="19"/>
@@ -3094,7 +3343,7 @@
     </row>
     <row r="33" spans="1:18">
       <c r="A33" s="9" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
@@ -3119,11 +3368,11 @@
         <v>0</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
@@ -3131,16 +3380,16 @@
         <v>2</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
@@ -3153,18 +3402,18 @@
         <v>1</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
@@ -3178,7 +3427,7 @@
     </row>
     <row r="37" spans="1:18">
       <c r="A37" s="9" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -3207,7 +3456,7 @@
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
@@ -3215,14 +3464,14 @@
         <v>2</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J38" s="1"/>
       <c r="K38" s="1" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
